--- a/utils/monday_sprint_sprint_2025-2.xlsx
+++ b/utils/monday_sprint_sprint_2025-2.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="158">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>29312</t>
+    <t>8088761943</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>19/12/2024</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>26/01/2025</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,7 +102,7 @@
     <t>Dezembro</t>
   </si>
   <si>
-    <t>29117</t>
+    <t>8105790926</t>
   </si>
   <si>
     <t>Correção</t>
@@ -117,7 +117,7 @@
     <t>Semana 4</t>
   </si>
   <si>
-    <t>29355</t>
+    <t>8209947939</t>
   </si>
   <si>
     <t>ATUALIZAÇÃO COLETA AUTOMATICA - SISTEMA INVOICE</t>
@@ -126,22 +126,28 @@
     <t>10/01/2025</t>
   </si>
   <si>
+    <t>20/01/2025</t>
+  </si>
+  <si>
     <t>Semana 2</t>
   </si>
   <si>
     <t>Janeiro</t>
   </si>
   <si>
-    <t>29199</t>
+    <t>8089120768</t>
   </si>
   <si>
     <t>Integração SPS X WMS</t>
   </si>
   <si>
+    <t>22/01/2025</t>
+  </si>
+  <si>
     <t>Implantação</t>
   </si>
   <si>
-    <t>28316</t>
+    <t>8095095674</t>
   </si>
   <si>
     <t>Movimentação da montagem do conjunto das Tampas (copy)</t>
@@ -150,7 +156,7 @@
     <t>20/12/2024</t>
   </si>
   <si>
-    <t>28708</t>
+    <t>8232353449</t>
   </si>
   <si>
     <t>Gerar registro no Benner (BLOCO K)</t>
@@ -162,7 +168,7 @@
     <t>13/01/2025</t>
   </si>
   <si>
-    <t>28847</t>
+    <t>8232353216</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -171,133 +177,172 @@
     <t>Criar lista de pré seleção  apontamento de acabamento</t>
   </si>
   <si>
-    <t>27180</t>
+    <t>8232353174</t>
   </si>
   <si>
     <t>Rateio tempos usinagem</t>
   </si>
   <si>
-    <t>23838</t>
+    <t>8232393250</t>
   </si>
   <si>
     <t>Ambiente de testes controle da pátio</t>
   </si>
   <si>
-    <t>29170</t>
+    <t>8232393074</t>
   </si>
   <si>
     <t>Melhorias apontamento de solda</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>8232393179</t>
   </si>
   <si>
     <t>Habilitar Tela eventos financeiros para Sueli - Julius - Entrega</t>
   </si>
   <si>
-    <t>27921</t>
+    <t>8232461537</t>
   </si>
   <si>
     <t>Desenvolver Aplicação Qlik Sense Horas de Apontamento - Fundição</t>
   </si>
   <si>
+    <t>8232461799</t>
+  </si>
+  <si>
     <t>Desenvolver Aplicação Qlik Sense Horas de Apontamento - Acabamento</t>
   </si>
   <si>
+    <t>8232461965</t>
+  </si>
+  <si>
     <t>Desenvolver Aplicação Qlik Sense Horas de Apontamento - Usinagem</t>
   </si>
   <si>
+    <t>8232462278</t>
+  </si>
+  <si>
     <t>Desenvolver Aplicação Qlik Sense Horas de Apontamento - Inspeção</t>
   </si>
   <si>
+    <t>8232353327</t>
+  </si>
+  <si>
     <t>Habilitar o sistema de apontamento dos manipuladores para o acabamento</t>
   </si>
   <si>
-    <t>29293</t>
+    <t>23/01/2025</t>
+  </si>
+  <si>
+    <t>8232393119</t>
   </si>
   <si>
     <t>MELHORIAS APONTAMENTO MANIPULADOR PEQUENO</t>
   </si>
   <si>
-    <t>26389</t>
+    <t>8232451148</t>
   </si>
   <si>
     <t>Controle Automático de n° sequencial de peça para ID de Bruto</t>
   </si>
   <si>
+    <t>16/01/2025</t>
+  </si>
+  <si>
+    <t>8337249349</t>
+  </si>
+  <si>
     <t>Movimentação da montagem do conjunto das Tampas (copy) (copy)</t>
   </si>
   <si>
     <t>27/01/2025</t>
   </si>
   <si>
-    <t>29254</t>
+    <t>8088964543</t>
   </si>
   <si>
     <t>PDI Eletrônico</t>
   </si>
   <si>
-    <t>29421</t>
+    <t>8209905252</t>
   </si>
   <si>
     <t>Altona || Sistema ERP || Reposição Exterior - 7.949</t>
   </si>
   <si>
-    <t>29409</t>
+    <t>14/01/2025</t>
+  </si>
+  <si>
+    <t>8209919500</t>
   </si>
   <si>
     <t>Altona || Sistema ERP || Compra de PF</t>
   </si>
   <si>
-    <t>29406</t>
+    <t>8209932730</t>
   </si>
   <si>
     <t>Projeto "SEGURANÇA O COMPROMISSO É MEU!" - adicionar a informação no apontamento da REB. VI/VII - se verificou a PMOV</t>
   </si>
   <si>
-    <t>29397</t>
+    <t>8209938972</t>
   </si>
   <si>
     <t>Sugestão de melhoria na proforma</t>
   </si>
   <si>
-    <t>29414</t>
+    <t>19/01/2025</t>
+  </si>
+  <si>
+    <t>8209911444</t>
   </si>
   <si>
     <t>Novos Status Invoice</t>
   </si>
   <si>
-    <t>29379</t>
+    <t>8209944704</t>
   </si>
   <si>
     <t>ERROS NOS % com risco de lançamentos errados</t>
   </si>
   <si>
-    <t>29334</t>
+    <t>8209955910</t>
   </si>
   <si>
     <t>Botão para liberar o saldo da nota no estoque</t>
   </si>
   <si>
-    <t>28975</t>
+    <t>8209977193</t>
   </si>
   <si>
     <t>MELHORIA NO SISTEMA DE ORÇAMENTO</t>
   </si>
   <si>
+    <t>8232473833</t>
+  </si>
+  <si>
     <t>Cotas - Tolerância mínima não está gravando</t>
   </si>
   <si>
+    <t>8232474736</t>
+  </si>
+  <si>
     <t>Tela wwpdi_inspecao - Validar campos decimais</t>
   </si>
   <si>
+    <t>8232475252</t>
+  </si>
+  <si>
     <t>Tela wwpdi_inspecao - Múltiplas sequências não está laudando a última sequência</t>
   </si>
   <si>
+    <t>8232475537</t>
+  </si>
+  <si>
     <t>Tela wwpdi_inspecao - Visualizar documento, desaparece opções do menu</t>
   </si>
   <si>
-    <t>29494</t>
+    <t>8246896724</t>
   </si>
   <si>
     <t>Nota promissória PROEX</t>
@@ -306,25 +351,25 @@
     <t>15/01/2025</t>
   </si>
   <si>
-    <t>28410</t>
+    <t>8232451089</t>
   </si>
   <si>
     <t>ENDEREÇAMENTO ALMOXARIFADO</t>
   </si>
   <si>
-    <t>25024</t>
+    <t>8251147281</t>
   </si>
   <si>
     <t>Indicador de "parada programada"  (OR022)</t>
   </si>
   <si>
-    <t>28798</t>
+    <t>8232451127</t>
   </si>
   <si>
     <t>Cenário Valorização 2</t>
   </si>
   <si>
-    <t>29666</t>
+    <t>8312905195</t>
   </si>
   <si>
     <t>Indefinido</t>
@@ -333,10 +378,7 @@
     <t>Entrada de componentes com ligas diferentes para mesmo conjunto</t>
   </si>
   <si>
-    <t>23/01/2025</t>
-  </si>
-  <si>
-    <t>28956</t>
+    <t>9531252210</t>
   </si>
   <si>
     <t>PDI eletrônico</t>
@@ -345,12 +387,12 @@
     <t>07/07/2025</t>
   </si>
   <si>
+    <t>06/07/2025</t>
+  </si>
+  <si>
     <t>Fazendo</t>
   </si>
   <si>
-    <t>Aberto</t>
-  </si>
-  <si>
     <t>Semana 1</t>
   </si>
   <si>
@@ -363,7 +405,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2025-2</t>
+    <t>Dez/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -1052,7 +1094,7 @@
         <v>36</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1061,15 +1103,15 @@
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1081,10 +1123,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>20</v>
@@ -1099,10 +1141,10 @@
         <v>23</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>26</v>
@@ -1116,7 +1158,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1128,10 +1170,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1143,13 +1185,13 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>26</v>
@@ -1163,7 +1205,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1175,13 +1217,13 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>21</v>
@@ -1190,7 +1232,7 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>24</v>
@@ -1202,45 +1244,45 @@
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="H8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1249,92 +1291,92 @@
         <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1343,15 +1385,15 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1363,13 +1405,13 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>21</v>
@@ -1378,10 +1420,10 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1390,45 +1432,45 @@
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1437,30 +1479,30 @@
         <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1472,10 +1514,10 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1484,30 +1526,30 @@
         <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1519,10 +1561,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1531,30 +1573,30 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1566,10 +1608,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1578,30 +1620,30 @@
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1613,10 +1655,10 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1625,30 +1667,30 @@
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1660,10 +1702,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1672,15 +1714,15 @@
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1692,10 +1734,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1707,27 +1749,27 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1739,13 +1781,13 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>21</v>
@@ -1754,27 +1796,27 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1786,10 +1828,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1801,13 +1843,13 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>26</v>
@@ -1816,12 +1858,12 @@
         <v>33</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1833,13 +1875,13 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>21</v>
@@ -1851,7 +1893,7 @@
         <v>23</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1868,7 +1910,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1880,10 +1922,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -1898,7 +1940,7 @@
         <v>36</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -1907,15 +1949,15 @@
         <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -1927,10 +1969,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -1945,7 +1987,7 @@
         <v>36</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -1954,15 +1996,15 @@
         <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -1974,10 +2016,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -1992,24 +2034,24 @@
         <v>36</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2021,10 +2063,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2039,7 +2081,7 @@
         <v>36</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2048,15 +2090,15 @@
         <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2068,10 +2110,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2086,7 +2128,7 @@
         <v>36</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2095,15 +2137,15 @@
         <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2115,10 +2157,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2133,7 +2175,7 @@
         <v>36</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2142,15 +2184,15 @@
         <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2162,10 +2204,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2180,7 +2222,7 @@
         <v>36</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2189,15 +2231,15 @@
         <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2209,10 +2251,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2236,45 +2278,45 @@
         <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J30" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2283,45 +2325,45 @@
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J31" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2330,45 +2372,45 @@
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J32" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2377,45 +2419,45 @@
         <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J33" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2424,30 +2466,30 @@
         <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2459,10 +2501,10 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2474,12 +2516,12 @@
         <v>27</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2491,10 +2533,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2506,10 +2548,10 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2518,33 +2560,33 @@
         <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>21</v>
@@ -2553,7 +2595,7 @@
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>24</v>
@@ -2568,12 +2610,12 @@
         <v>27</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2585,10 +2627,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2600,10 +2642,10 @@
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
@@ -2612,33 +2654,33 @@
         <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>21</v>
@@ -2647,10 +2689,10 @@
         <v>22</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>25</v>
@@ -2662,27 +2704,27 @@
         <v>33</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -2694,22 +2736,22 @@
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>124</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>111</v>
+        <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -2725,23 +2767,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="E2" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -2749,16 +2791,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2769,7 +2811,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>10.03</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -2777,7 +2819,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -2790,7 +2832,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K23">
         <v>7</v>
@@ -2798,7 +2840,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -2829,12 +2871,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="B2">
         <v>38</v>
@@ -2848,7 +2890,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>10.03</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -2858,25 +2900,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2893,13 +2935,13 @@
         <v>19</v>
       </c>
       <c r="G10" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -2911,21 +2953,21 @@
         <v>30</v>
       </c>
       <c r="P10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q10">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E11">
         <v>16</v>
       </c>
       <c r="G11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H11">
         <v>14</v>
@@ -2934,10 +2976,10 @@
         <v>26</v>
       </c>
       <c r="K11">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M11" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -2946,7 +2988,7 @@
         <v>27</v>
       </c>
       <c r="Q11">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
@@ -2963,13 +3005,13 @@
         <v>24</v>
       </c>
       <c r="J12" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="K12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -2978,24 +3020,24 @@
         <v>33</v>
       </c>
       <c r="Q12">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="N13">
         <v>1</v>
@@ -3003,13 +3045,13 @@
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N14">
         <v>7</v>
@@ -3017,7 +3059,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3025,7 +3067,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3033,7 +3075,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3041,10 +3083,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -3052,7 +3094,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3060,142 +3102,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>121</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>531</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>53</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>55</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
